--- a/backend/data/financials_by_company/1835.SR.xlsx
+++ b/backend/data/financials_by_company/1835.SR.xlsx
@@ -3249,25 +3249,19 @@
           <t>Riyadh</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>12333</t>
-        </is>
+      <c r="D2" t="n">
+        <v>12333</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>920000199</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>920000199</t>
-        </is>
+      <c r="F2" t="n">
+        <v>920000199</v>
+      </c>
+      <c r="G2" t="n">
+        <v>920000199</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
